--- a/final_transactions_database.xlsx
+++ b/final_transactions_database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yusra Faisal\OneDrive\Desktop\sbb\social_banking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756B09EB-F779-493B-A107-D27C0F9B2EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D04A6C-54A4-4055-AC89-CC5C408D297C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="555" windowWidth="11355" windowHeight="10260" xr2:uid="{B85DD6FC-CB01-42FE-9FC1-227D3A58D588}"/>
+    <workbookView minimized="1" xWindow="660" yWindow="675" windowWidth="11355" windowHeight="10260" xr2:uid="{B85DD6FC-CB01-42FE-9FC1-227D3A58D588}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -614,7 +614,7 @@
         <v>96293.38</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1001</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>57727.81</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1001</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>43867.38</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1001</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>42209.57</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>1001</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>39233.269999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>1001</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>36372.83</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>1003</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>97049.52</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>1003</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>94301.15</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>1003</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>92384.51</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>1003</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>89906.78</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>1003</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>88280.21</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>1003</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>85745.14</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>1003</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>83189.09</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>1003</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>81531.28</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1003</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>78554.98</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1003</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>75676.210000000006</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>1003</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>73452.490000000005</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>1003</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>75744.11</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>1003</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>73161.03</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>1003</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>70824.22</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>1003</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>68928.3</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>1003</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>66527.45</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>1003</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>64963.03</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>1003</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>62520.5</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1003</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>60430.18</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>1003</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>58316.85</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1003</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>56669.01</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>1003</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>53711.56</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>1003</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>52022.05</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>1003</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>49987.17</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>1003</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>47903.43</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>1003</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>46280.55</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>1003</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>43802.879999999997</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1003</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>41922.22</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1003</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>39399.199999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>1003</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>36482.910000000003</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>1003</v>
       </c>
@@ -4589,7 +4589,12 @@
   <autoFilter ref="A1:I121" xr:uid="{F8DFEDB2-E4B2-4B56-A9AA-9863548A529F}">
     <filterColumn colId="0">
       <filters>
-        <filter val="1003"/>
+        <filter val="1001"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Travel"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/final_transactions_database.xlsx
+++ b/final_transactions_database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yusra Faisal\OneDrive\Desktop\sbb\social_banking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D04A6C-54A4-4055-AC89-CC5C408D297C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7D0833-8BE0-45B2-AB2C-931910ED8F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="660" yWindow="675" windowWidth="11355" windowHeight="10260" xr2:uid="{B85DD6FC-CB01-42FE-9FC1-227D3A58D588}"/>
+    <workbookView xWindow="315" yWindow="615" windowWidth="11355" windowHeight="10260" xr2:uid="{B85DD6FC-CB01-42FE-9FC1-227D3A58D588}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -614,7 +614,7 @@
         <v>96293.38</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1001</v>
       </c>
@@ -846,7 +846,7 @@
         <v>77702.61</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1001</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>57727.81</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1001</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>43867.38</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1001</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>42209.57</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>1001</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>39233.269999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>1001</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>36354.5</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>1001</v>
       </c>
@@ -4592,9 +4592,9 @@
         <filter val="1001"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="4">
+    <filterColumn colId="3">
       <filters>
-        <filter val="Travel"/>
+        <filter val="McDonalds"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/final_transactions_database.xlsx
+++ b/final_transactions_database.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yusra Faisal\OneDrive\Desktop\sbb\social_banking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7D0833-8BE0-45B2-AB2C-931910ED8F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB08B17-BC79-4BEA-838A-FC6B1A9BF500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="315" yWindow="615" windowWidth="11355" windowHeight="10260" xr2:uid="{B85DD6FC-CB01-42FE-9FC1-227D3A58D588}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B85DD6FC-CB01-42FE-9FC1-227D3A58D588}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$121</definedName>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="42">
   <si>
     <t>account_number</t>
   </si>
@@ -140,6 +141,30 @@
   <si>
     <t>Personal Transfer</t>
   </si>
+  <si>
+    <t>account_currency</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>usd</t>
+  </si>
+  <si>
+    <t>transaction_amount</t>
+  </si>
+  <si>
+    <t>transaction_currency</t>
+  </si>
+  <si>
+    <t>pkr</t>
+  </si>
+  <si>
+    <t>withdrawal</t>
+  </si>
+  <si>
+    <t>aed</t>
+  </si>
 </sst>
 </file>
 
@@ -200,12 +225,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,7 +551,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8DFEDB2-E4B2-4B56-A9AA-9863548A529F}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I304"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -556,7 +586,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -585,7 +615,7 @@
         <v>97916.26</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1001</v>
       </c>
@@ -614,7 +644,7 @@
         <v>96293.38</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1001</v>
       </c>
@@ -643,7 +673,7 @@
         <v>93815.71</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1001</v>
       </c>
@@ -672,7 +702,7 @@
         <v>91935.05</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1001</v>
       </c>
@@ -701,7 +731,7 @@
         <v>89412.03</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1001</v>
       </c>
@@ -730,7 +760,7 @@
         <v>86495.74</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1001</v>
       </c>
@@ -759,7 +789,7 @@
         <v>83755.25</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1001</v>
       </c>
@@ -788,7 +818,7 @@
         <v>81899.17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1001</v>
       </c>
@@ -817,7 +847,7 @@
         <v>79606.69</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1001</v>
       </c>
@@ -875,7 +905,7 @@
         <v>74708.73</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1001</v>
       </c>
@@ -904,7 +934,7 @@
         <v>72727.64</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1001</v>
       </c>
@@ -933,7 +963,7 @@
         <v>75333.759999999995</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1001</v>
       </c>
@@ -962,7 +992,7 @@
         <v>73048.03</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1001</v>
       </c>
@@ -991,7 +1021,7 @@
         <v>70235.009999999995</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1001</v>
       </c>
@@ -1020,7 +1050,7 @@
         <v>68679.990000000005</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1001</v>
       </c>
@@ -1049,7 +1079,7 @@
         <v>66861.25</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1001</v>
       </c>
@@ -1078,7 +1108,7 @@
         <v>64618.8</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1001</v>
       </c>
@@ -1107,7 +1137,7 @@
         <v>62582.23</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1001</v>
       </c>
@@ -1136,7 +1166,7 @@
         <v>60678.29</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1001</v>
       </c>
@@ -1165,7 +1195,7 @@
         <v>57727.81</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1001</v>
       </c>
@@ -1194,7 +1224,7 @@
         <v>54979.44</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1001</v>
       </c>
@@ -1223,7 +1253,7 @@
         <v>53062.8</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1001</v>
       </c>
@@ -1252,7 +1282,7 @@
         <v>50585.07</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1001</v>
       </c>
@@ -1281,7 +1311,7 @@
         <v>48958.5</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1001</v>
       </c>
@@ -1310,7 +1340,7 @@
         <v>46423.43</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>1001</v>
       </c>
@@ -1339,7 +1369,7 @@
         <v>43867.38</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1001</v>
       </c>
@@ -1368,7 +1398,7 @@
         <v>42209.57</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>1001</v>
       </c>
@@ -1397,7 +1427,7 @@
         <v>39233.269999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>1001</v>
       </c>
@@ -1455,7 +1485,7 @@
         <v>34130.78</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>1001</v>
       </c>
@@ -1484,7 +1514,7 @@
         <v>31839.16</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>1001</v>
       </c>
@@ -1513,7 +1543,7 @@
         <v>29256.080000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>1002</v>
       </c>
@@ -1542,7 +1572,7 @@
         <v>97663.19</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>1002</v>
       </c>
@@ -1571,7 +1601,7 @@
         <v>95767.27</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>1002</v>
       </c>
@@ -1600,7 +1630,7 @@
         <v>93366.42</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1002</v>
       </c>
@@ -1629,7 +1659,7 @@
         <v>91802</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>1002</v>
       </c>
@@ -1658,7 +1688,7 @@
         <v>89359.47</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1002</v>
       </c>
@@ -1687,7 +1717,7 @@
         <v>91449.79</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1002</v>
       </c>
@@ -1716,7 +1746,7 @@
         <v>89336.46</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>1002</v>
       </c>
@@ -1745,7 +1775,7 @@
         <v>87688.62</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>1002</v>
       </c>
@@ -1774,7 +1804,7 @@
         <v>84731.17</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>1002</v>
       </c>
@@ -1803,7 +1833,7 @@
         <v>83041.66</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>1002</v>
       </c>
@@ -1832,7 +1862,7 @@
         <v>81006.78</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>1002</v>
       </c>
@@ -1861,7 +1891,7 @@
         <v>78923.039999999994</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1002</v>
       </c>
@@ -1890,7 +1920,7 @@
         <v>77300.160000000003</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>1002</v>
       </c>
@@ -1919,7 +1949,7 @@
         <v>74822.490000000005</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>1002</v>
       </c>
@@ -1948,7 +1978,7 @@
         <v>72941.83</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>1002</v>
       </c>
@@ -1977,7 +2007,7 @@
         <v>70418.81</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>1002</v>
       </c>
@@ -2006,7 +2036,7 @@
         <v>67402.52</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>1002</v>
       </c>
@@ -2035,7 +2065,7 @@
         <v>64662.03</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>1002</v>
       </c>
@@ -2064,7 +2094,7 @@
         <v>62805.95</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>1002</v>
       </c>
@@ -2093,7 +2123,7 @@
         <v>60513.47</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>1002</v>
       </c>
@@ -2122,7 +2152,7 @@
         <v>58609.39</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>1002</v>
       </c>
@@ -2151,7 +2181,7 @@
         <v>55615.51</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>1002</v>
       </c>
@@ -2180,7 +2210,7 @@
         <v>53634.42</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>1002</v>
       </c>
@@ -2209,7 +2239,7 @@
         <v>51028.3</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>1002</v>
       </c>
@@ -2238,7 +2268,7 @@
         <v>48742.57</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>1002</v>
       </c>
@@ -2267,7 +2297,7 @@
         <v>45929.55</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1002</v>
       </c>
@@ -2296,7 +2326,7 @@
         <v>44374.53</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1002</v>
       </c>
@@ -2325,7 +2355,7 @@
         <v>42555.79</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>1002</v>
       </c>
@@ -2354,7 +2384,7 @@
         <v>40313.339999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>1002</v>
       </c>
@@ -2383,7 +2413,7 @@
         <v>38276.769999999997</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>1002</v>
       </c>
@@ -2412,7 +2442,7 @@
         <v>36372.83</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>1003</v>
       </c>
@@ -2441,7 +2471,7 @@
         <v>97049.52</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>1003</v>
       </c>
@@ -2470,7 +2500,7 @@
         <v>94301.15</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>1003</v>
       </c>
@@ -2499,7 +2529,7 @@
         <v>92384.51</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>1003</v>
       </c>
@@ -2528,7 +2558,7 @@
         <v>89906.78</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>1003</v>
       </c>
@@ -2557,7 +2587,7 @@
         <v>88280.21</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>1003</v>
       </c>
@@ -2586,7 +2616,7 @@
         <v>85745.14</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>1003</v>
       </c>
@@ -2615,7 +2645,7 @@
         <v>83189.09</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>1003</v>
       </c>
@@ -2644,7 +2674,7 @@
         <v>81531.28</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1003</v>
       </c>
@@ -2673,7 +2703,7 @@
         <v>78554.98</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1003</v>
       </c>
@@ -2702,7 +2732,7 @@
         <v>75676.210000000006</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>1003</v>
       </c>
@@ -2731,7 +2761,7 @@
         <v>73452.490000000005</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>1003</v>
       </c>
@@ -2760,7 +2790,7 @@
         <v>75744.11</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>1003</v>
       </c>
@@ -2789,7 +2819,7 @@
         <v>73161.03</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>1003</v>
       </c>
@@ -2818,7 +2848,7 @@
         <v>70824.22</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>1003</v>
       </c>
@@ -2847,7 +2877,7 @@
         <v>68928.3</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>1003</v>
       </c>
@@ -2876,7 +2906,7 @@
         <v>66527.45</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>1003</v>
       </c>
@@ -2905,7 +2935,7 @@
         <v>64963.03</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>1003</v>
       </c>
@@ -2934,7 +2964,7 @@
         <v>62520.5</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1003</v>
       </c>
@@ -2963,7 +2993,7 @@
         <v>60430.18</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>1003</v>
       </c>
@@ -2992,7 +3022,7 @@
         <v>58316.85</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1003</v>
       </c>
@@ -3021,7 +3051,7 @@
         <v>56669.01</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>1003</v>
       </c>
@@ -3050,7 +3080,7 @@
         <v>53711.56</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>1003</v>
       </c>
@@ -3079,7 +3109,7 @@
         <v>52022.05</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>1003</v>
       </c>
@@ -3108,7 +3138,7 @@
         <v>49987.17</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>1003</v>
       </c>
@@ -3137,7 +3167,7 @@
         <v>47903.43</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>1003</v>
       </c>
@@ -3166,7 +3196,7 @@
         <v>46280.55</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>1003</v>
       </c>
@@ -3195,7 +3225,7 @@
         <v>43802.879999999997</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1003</v>
       </c>
@@ -3224,7 +3254,7 @@
         <v>41922.22</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1003</v>
       </c>
@@ -3253,7 +3283,7 @@
         <v>39399.199999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>1003</v>
       </c>
@@ -3282,7 +3312,7 @@
         <v>36482.910000000003</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>1003</v>
       </c>
@@ -3311,7 +3341,7 @@
         <v>33742.42</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>1004</v>
       </c>
@@ -3340,7 +3370,7 @@
         <v>98143.92</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1004</v>
       </c>
@@ -3369,7 +3399,7 @@
         <v>95851.44</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>1004</v>
       </c>
@@ -3398,7 +3428,7 @@
         <v>93947.36</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>1004</v>
       </c>
@@ -3427,7 +3457,7 @@
         <v>90953.48</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>1004</v>
       </c>
@@ -3456,7 +3486,7 @@
         <v>88972.39</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1004</v>
       </c>
@@ -3485,7 +3515,7 @@
         <v>86366.27</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>1004</v>
       </c>
@@ -3514,7 +3544,7 @@
         <v>84080.54</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>1004</v>
       </c>
@@ -3543,7 +3573,7 @@
         <v>81267.520000000004</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>1004</v>
       </c>
@@ -3572,7 +3602,7 @@
         <v>79712.5</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>1004</v>
       </c>
@@ -3601,7 +3631,7 @@
         <v>81531.240000000005</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>1004</v>
       </c>
@@ -3630,7 +3660,7 @@
         <v>79288.789999999994</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>1004</v>
       </c>
@@ -3659,7 +3689,7 @@
         <v>77252.22</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>1004</v>
       </c>
@@ -3688,7 +3718,7 @@
         <v>75348.28</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1004</v>
       </c>
@@ -3717,7 +3747,7 @@
         <v>72397.8</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>1004</v>
       </c>
@@ -3746,7 +3776,7 @@
         <v>69649.429999999993</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>1004</v>
       </c>
@@ -3775,7 +3805,7 @@
         <v>67732.789999999994</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>1004</v>
       </c>
@@ -3804,7 +3834,7 @@
         <v>65255.06</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1004</v>
       </c>
@@ -3833,7 +3863,7 @@
         <v>63628.49</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>1004</v>
       </c>
@@ -3862,7 +3892,7 @@
         <v>61093.42</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>1004</v>
       </c>
@@ -3891,7 +3921,7 @@
         <v>58537.37</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>1004</v>
       </c>
@@ -3920,7 +3950,7 @@
         <v>56879.56</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>1004</v>
       </c>
@@ -3949,7 +3979,7 @@
         <v>53903.26</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>1004</v>
       </c>
@@ -3978,7 +4008,7 @@
         <v>51024.49</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>1004</v>
       </c>
@@ -4007,7 +4037,7 @@
         <v>48800.77</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>1004</v>
       </c>
@@ -4586,18 +4616,3630 @@
       <c r="B304" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I121" xr:uid="{F8DFEDB2-E4B2-4B56-A9AA-9863548A529F}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="1001"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="McDonalds"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{951307EC-006A-4378-9169-FDB411FF2A86}">
+  <dimension ref="A1:K124"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="11" width="17.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1234</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="4">
+        <v>45855</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="3">
+        <v>50</v>
+      </c>
+      <c r="H2" s="3">
+        <v>50</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>1234</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="4">
+        <v>45855</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="3">
+        <v>600</v>
+      </c>
+      <c r="H3" s="3">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>1234</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="4">
+        <v>45855</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="3">
+        <v>80</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1001</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>50.35</v>
+      </c>
+      <c r="H5">
+        <v>2083.7399999999998</v>
+      </c>
+      <c r="J5">
+        <v>1949.65</v>
+      </c>
+      <c r="K5">
+        <v>97916.26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1001</v>
+      </c>
+      <c r="C6" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>84.69</v>
+      </c>
+      <c r="H6">
+        <v>1622.88</v>
+      </c>
+      <c r="J6">
+        <v>1864.96</v>
+      </c>
+      <c r="K6">
+        <v>96293.38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1001</v>
+      </c>
+      <c r="C7" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <v>21.85</v>
+      </c>
+      <c r="H7">
+        <v>2477.67</v>
+      </c>
+      <c r="J7">
+        <v>1843.11</v>
+      </c>
+      <c r="K7">
+        <v>93815.71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1001</v>
+      </c>
+      <c r="C8" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8">
+        <v>75.38</v>
+      </c>
+      <c r="H8">
+        <v>1880.66</v>
+      </c>
+      <c r="J8">
+        <v>1767.73</v>
+      </c>
+      <c r="K8">
+        <v>91935.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1001</v>
+      </c>
+      <c r="C9" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9">
+        <v>17.75</v>
+      </c>
+      <c r="H9">
+        <v>2523.02</v>
+      </c>
+      <c r="J9">
+        <v>1749.98</v>
+      </c>
+      <c r="K9">
+        <v>89412.03</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1001</v>
+      </c>
+      <c r="C10" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>21.49</v>
+      </c>
+      <c r="H10">
+        <v>2916.29</v>
+      </c>
+      <c r="J10">
+        <v>1728.49</v>
+      </c>
+      <c r="K10">
+        <v>86495.74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1001</v>
+      </c>
+      <c r="C11" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11">
+        <v>24.1</v>
+      </c>
+      <c r="H11">
+        <v>2740.49</v>
+      </c>
+      <c r="J11">
+        <v>1704.39</v>
+      </c>
+      <c r="K11">
+        <v>83755.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1001</v>
+      </c>
+      <c r="C12" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12">
+        <v>11.12</v>
+      </c>
+      <c r="H12">
+        <v>1856.08</v>
+      </c>
+      <c r="J12">
+        <v>1693.27</v>
+      </c>
+      <c r="K12">
+        <v>81899.17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1001</v>
+      </c>
+      <c r="C13" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13">
+        <v>17.52</v>
+      </c>
+      <c r="H13">
+        <v>2292.48</v>
+      </c>
+      <c r="J13">
+        <v>1675.75</v>
+      </c>
+      <c r="K13">
+        <v>79606.69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1001</v>
+      </c>
+      <c r="C14" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14">
+        <v>18.260000000000002</v>
+      </c>
+      <c r="H14">
+        <v>1904.08</v>
+      </c>
+      <c r="J14">
+        <v>1657.49</v>
+      </c>
+      <c r="K14">
+        <v>77702.61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1001</v>
+      </c>
+      <c r="C15" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15">
+        <v>22.08</v>
+      </c>
+      <c r="H15">
+        <v>2993.88</v>
+      </c>
+      <c r="J15">
+        <v>1635.41</v>
+      </c>
+      <c r="K15">
+        <v>74708.73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1001</v>
+      </c>
+      <c r="C16" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16">
+        <v>16.77</v>
+      </c>
+      <c r="H16">
+        <v>1981.09</v>
+      </c>
+      <c r="J16">
+        <v>1618.64</v>
+      </c>
+      <c r="K16">
+        <v>72727.64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1001</v>
+      </c>
+      <c r="C17" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17">
+        <v>4000</v>
+      </c>
+      <c r="H17">
+        <v>2606.12</v>
+      </c>
+      <c r="J17">
+        <v>5618.64</v>
+      </c>
+      <c r="K17">
+        <v>75333.759999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1001</v>
+      </c>
+      <c r="C18" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18">
+        <v>19.13</v>
+      </c>
+      <c r="H18">
+        <v>2285.73</v>
+      </c>
+      <c r="J18">
+        <v>5599.51</v>
+      </c>
+      <c r="K18">
+        <v>73048.03</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1001</v>
+      </c>
+      <c r="C19" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19">
+        <v>22.82</v>
+      </c>
+      <c r="H19">
+        <v>2813.02</v>
+      </c>
+      <c r="J19">
+        <v>5576.69</v>
+      </c>
+      <c r="K19">
+        <v>70235.009999999995</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1001</v>
+      </c>
+      <c r="C20" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20">
+        <v>14.87</v>
+      </c>
+      <c r="H20">
+        <v>1555.02</v>
+      </c>
+      <c r="J20">
+        <v>5561.82</v>
+      </c>
+      <c r="K20">
+        <v>68679.990000000005</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1001</v>
+      </c>
+      <c r="C21" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21">
+        <v>23.71</v>
+      </c>
+      <c r="H21">
+        <v>1818.74</v>
+      </c>
+      <c r="J21">
+        <v>5538.11</v>
+      </c>
+      <c r="K21">
+        <v>66861.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1001</v>
+      </c>
+      <c r="C22" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22">
+        <v>77.86</v>
+      </c>
+      <c r="H22">
+        <v>2242.4499999999998</v>
+      </c>
+      <c r="J22">
+        <v>5460.25</v>
+      </c>
+      <c r="K22">
+        <v>64618.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1001</v>
+      </c>
+      <c r="C23" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23">
+        <v>21.03</v>
+      </c>
+      <c r="H23">
+        <v>2036.57</v>
+      </c>
+      <c r="J23">
+        <v>5439.22</v>
+      </c>
+      <c r="K23">
+        <v>62582.23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1001</v>
+      </c>
+      <c r="C24" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24">
+        <v>12</v>
+      </c>
+      <c r="H24">
+        <v>1903.94</v>
+      </c>
+      <c r="J24">
+        <v>5427.22</v>
+      </c>
+      <c r="K24">
+        <v>60678.29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>1001</v>
+      </c>
+      <c r="C25" s="2">
+        <v>45813</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25">
+        <v>22.99</v>
+      </c>
+      <c r="H25">
+        <v>2950.48</v>
+      </c>
+      <c r="J25">
+        <v>5404.23</v>
+      </c>
+      <c r="K25">
+        <v>57727.81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>1001</v>
+      </c>
+      <c r="C26" s="2">
+        <v>45813</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26">
+        <v>20.65</v>
+      </c>
+      <c r="H26">
+        <v>2748.37</v>
+      </c>
+      <c r="J26">
+        <v>5383.58</v>
+      </c>
+      <c r="K26">
+        <v>54979.44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>1001</v>
+      </c>
+      <c r="C27" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" t="s">
+        <v>30</v>
+      </c>
+      <c r="G27">
+        <v>81.93</v>
+      </c>
+      <c r="H27">
+        <v>1916.64</v>
+      </c>
+      <c r="J27">
+        <v>5301.65</v>
+      </c>
+      <c r="K27">
+        <v>53062.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>1001</v>
+      </c>
+      <c r="C28" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" t="s">
+        <v>30</v>
+      </c>
+      <c r="G28">
+        <v>94.02</v>
+      </c>
+      <c r="H28">
+        <v>2477.73</v>
+      </c>
+      <c r="J28">
+        <v>5207.63</v>
+      </c>
+      <c r="K28">
+        <v>50585.07</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>1001</v>
+      </c>
+      <c r="C29" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29">
+        <v>24.05</v>
+      </c>
+      <c r="H29">
+        <v>1626.57</v>
+      </c>
+      <c r="J29">
+        <v>5183.58</v>
+      </c>
+      <c r="K29">
+        <v>48958.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>1001</v>
+      </c>
+      <c r="C30" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30">
+        <v>20.88</v>
+      </c>
+      <c r="H30">
+        <v>2535.0700000000002</v>
+      </c>
+      <c r="J30">
+        <v>5162.7</v>
+      </c>
+      <c r="K30">
+        <v>46423.43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>1001</v>
+      </c>
+      <c r="C31" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31">
+        <v>20.89</v>
+      </c>
+      <c r="H31">
+        <v>2556.0500000000002</v>
+      </c>
+      <c r="J31">
+        <v>5141.8100000000004</v>
+      </c>
+      <c r="K31">
+        <v>43867.38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>1001</v>
+      </c>
+      <c r="C32" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32">
+        <v>23</v>
+      </c>
+      <c r="H32">
+        <v>1657.81</v>
+      </c>
+      <c r="J32">
+        <v>5118.8100000000004</v>
+      </c>
+      <c r="K32">
+        <v>42209.57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>1001</v>
+      </c>
+      <c r="C33" s="2">
+        <v>45815</v>
+      </c>
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33">
+        <v>21.11</v>
+      </c>
+      <c r="H33">
+        <v>2976.3</v>
+      </c>
+      <c r="J33">
+        <v>5097.7</v>
+      </c>
+      <c r="K33">
+        <v>39233.269999999997</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>1001</v>
+      </c>
+      <c r="C34" s="2">
+        <v>45815</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34">
+        <v>13.42</v>
+      </c>
+      <c r="H34">
+        <v>2878.77</v>
+      </c>
+      <c r="J34">
+        <v>5084.28</v>
+      </c>
+      <c r="K34">
+        <v>36354.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>1001</v>
+      </c>
+      <c r="C35" s="2">
+        <v>45815</v>
+      </c>
+      <c r="D35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35">
+        <v>71.88</v>
+      </c>
+      <c r="H35">
+        <v>2223.7199999999998</v>
+      </c>
+      <c r="J35">
+        <v>5012.3999999999996</v>
+      </c>
+      <c r="K35">
+        <v>34130.78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>1001</v>
+      </c>
+      <c r="C36" s="2">
+        <v>45816</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36">
+        <v>12</v>
+      </c>
+      <c r="H36">
+        <v>2291.62</v>
+      </c>
+      <c r="J36">
+        <v>5000.3999999999996</v>
+      </c>
+      <c r="K36">
+        <v>31839.16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>1001</v>
+      </c>
+      <c r="C37" s="2">
+        <v>45817</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" t="s">
+        <v>32</v>
+      </c>
+      <c r="F37" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37">
+        <v>20</v>
+      </c>
+      <c r="H37">
+        <v>2583.08</v>
+      </c>
+      <c r="J37">
+        <v>4980.3999999999996</v>
+      </c>
+      <c r="K37">
+        <v>29256.080000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>1002</v>
+      </c>
+      <c r="C38" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38">
+        <v>94.73</v>
+      </c>
+      <c r="H38">
+        <v>2336.81</v>
+      </c>
+      <c r="J38">
+        <v>1905.27</v>
+      </c>
+      <c r="K38">
+        <v>97663.19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>1002</v>
+      </c>
+      <c r="C39" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39">
+        <v>36.549999999999997</v>
+      </c>
+      <c r="H39">
+        <v>1895.92</v>
+      </c>
+      <c r="J39">
+        <v>1868.72</v>
+      </c>
+      <c r="K39">
+        <v>95767.27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>1002</v>
+      </c>
+      <c r="C40" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D40" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40">
+        <v>12.21</v>
+      </c>
+      <c r="H40">
+        <v>2400.85</v>
+      </c>
+      <c r="J40">
+        <v>1856.51</v>
+      </c>
+      <c r="K40">
+        <v>93366.42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>1002</v>
+      </c>
+      <c r="C41" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41">
+        <v>17.88</v>
+      </c>
+      <c r="H41">
+        <v>1564.42</v>
+      </c>
+      <c r="J41">
+        <v>1838.63</v>
+      </c>
+      <c r="K41">
+        <v>91802</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>1002</v>
+      </c>
+      <c r="C42" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" t="s">
+        <v>17</v>
+      </c>
+      <c r="G42">
+        <v>23.82</v>
+      </c>
+      <c r="H42">
+        <v>2442.5300000000002</v>
+      </c>
+      <c r="J42">
+        <v>1814.81</v>
+      </c>
+      <c r="K42">
+        <v>89359.47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>1002</v>
+      </c>
+      <c r="C43" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D43" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" t="s">
+        <v>26</v>
+      </c>
+      <c r="F43" t="s">
+        <v>27</v>
+      </c>
+      <c r="G43">
+        <v>4000</v>
+      </c>
+      <c r="H43">
+        <v>2090.3200000000002</v>
+      </c>
+      <c r="J43">
+        <v>5814.81</v>
+      </c>
+      <c r="K43">
+        <v>91449.79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>1002</v>
+      </c>
+      <c r="C44" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44">
+        <v>23.96</v>
+      </c>
+      <c r="H44">
+        <v>2113.33</v>
+      </c>
+      <c r="J44">
+        <v>5790.85</v>
+      </c>
+      <c r="K44">
+        <v>89336.46</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>1002</v>
+      </c>
+      <c r="C45" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45">
+        <v>23.9</v>
+      </c>
+      <c r="H45">
+        <v>1647.84</v>
+      </c>
+      <c r="J45">
+        <v>5766.95</v>
+      </c>
+      <c r="K45">
+        <v>87688.62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>1002</v>
+      </c>
+      <c r="C46" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D46" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46">
+        <v>17.46</v>
+      </c>
+      <c r="H46">
+        <v>2957.45</v>
+      </c>
+      <c r="J46">
+        <v>5749.49</v>
+      </c>
+      <c r="K46">
+        <v>84731.17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>1002</v>
+      </c>
+      <c r="C47" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D47" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47">
+        <v>96.74</v>
+      </c>
+      <c r="H47">
+        <v>1689.51</v>
+      </c>
+      <c r="J47">
+        <v>5652.75</v>
+      </c>
+      <c r="K47">
+        <v>83041.66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1002</v>
+      </c>
+      <c r="C48" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48">
+        <v>14.83</v>
+      </c>
+      <c r="H48">
+        <v>2034.88</v>
+      </c>
+      <c r="J48">
+        <v>5637.92</v>
+      </c>
+      <c r="K48">
+        <v>81006.78</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>1002</v>
+      </c>
+      <c r="C49" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" t="s">
+        <v>17</v>
+      </c>
+      <c r="G49">
+        <v>22.52</v>
+      </c>
+      <c r="H49">
+        <v>2083.7399999999998</v>
+      </c>
+      <c r="J49">
+        <v>5615.4</v>
+      </c>
+      <c r="K49">
+        <v>78923.039999999994</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>1002</v>
+      </c>
+      <c r="C50" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" t="s">
+        <v>22</v>
+      </c>
+      <c r="F50" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50">
+        <v>13.79</v>
+      </c>
+      <c r="H50">
+        <v>1622.88</v>
+      </c>
+      <c r="J50">
+        <v>5601.61</v>
+      </c>
+      <c r="K50">
+        <v>77300.160000000003</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>1002</v>
+      </c>
+      <c r="C51" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D51" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51">
+        <v>21.57</v>
+      </c>
+      <c r="H51">
+        <v>2477.67</v>
+      </c>
+      <c r="J51">
+        <v>5580.04</v>
+      </c>
+      <c r="K51">
+        <v>74822.490000000005</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>1002</v>
+      </c>
+      <c r="C52" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" t="s">
+        <v>20</v>
+      </c>
+      <c r="F52" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52">
+        <v>21.28</v>
+      </c>
+      <c r="H52">
+        <v>1880.66</v>
+      </c>
+      <c r="J52">
+        <v>5558.76</v>
+      </c>
+      <c r="K52">
+        <v>72941.83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>1002</v>
+      </c>
+      <c r="C53" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" t="s">
+        <v>28</v>
+      </c>
+      <c r="F53" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53">
+        <v>60.97</v>
+      </c>
+      <c r="H53">
+        <v>2523.02</v>
+      </c>
+      <c r="J53">
+        <v>5497.79</v>
+      </c>
+      <c r="K53">
+        <v>70418.81</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1002</v>
+      </c>
+      <c r="C54" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" t="s">
+        <v>17</v>
+      </c>
+      <c r="G54">
+        <v>57.79</v>
+      </c>
+      <c r="H54">
+        <v>2916.29</v>
+      </c>
+      <c r="J54">
+        <v>5440</v>
+      </c>
+      <c r="K54">
+        <v>67402.52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>1002</v>
+      </c>
+      <c r="C55" s="2">
+        <v>45813</v>
+      </c>
+      <c r="D55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55">
+        <v>12.69</v>
+      </c>
+      <c r="H55">
+        <v>2740.49</v>
+      </c>
+      <c r="J55">
+        <v>5427.31</v>
+      </c>
+      <c r="K55">
+        <v>64662.03</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>1002</v>
+      </c>
+      <c r="C56" s="2">
+        <v>45813</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" t="s">
+        <v>17</v>
+      </c>
+      <c r="G56">
+        <v>96.64</v>
+      </c>
+      <c r="H56">
+        <v>1856.08</v>
+      </c>
+      <c r="J56">
+        <v>5330.67</v>
+      </c>
+      <c r="K56">
+        <v>62805.95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>1002</v>
+      </c>
+      <c r="C57" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" t="s">
+        <v>20</v>
+      </c>
+      <c r="F57" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57">
+        <v>55.95</v>
+      </c>
+      <c r="H57">
+        <v>2292.48</v>
+      </c>
+      <c r="J57">
+        <v>5274.72</v>
+      </c>
+      <c r="K57">
+        <v>60513.47</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>1002</v>
+      </c>
+      <c r="C58" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" t="s">
+        <v>29</v>
+      </c>
+      <c r="F58" t="s">
+        <v>30</v>
+      </c>
+      <c r="G58">
+        <v>11.48</v>
+      </c>
+      <c r="H58">
+        <v>1904.08</v>
+      </c>
+      <c r="J58">
+        <v>5263.24</v>
+      </c>
+      <c r="K58">
+        <v>58609.39</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>1002</v>
+      </c>
+      <c r="C59" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D59" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59">
+        <v>15.98</v>
+      </c>
+      <c r="H59">
+        <v>2993.88</v>
+      </c>
+      <c r="J59">
+        <v>5247.26</v>
+      </c>
+      <c r="K59">
+        <v>55615.51</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>1002</v>
+      </c>
+      <c r="C60" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="H60">
+        <v>1981.09</v>
+      </c>
+      <c r="J60">
+        <v>5230.2700000000004</v>
+      </c>
+      <c r="K60">
+        <v>53634.42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>1002</v>
+      </c>
+      <c r="C61" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D61" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" t="s">
+        <v>20</v>
+      </c>
+      <c r="F61" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61">
+        <v>17.07</v>
+      </c>
+      <c r="H61">
+        <v>2606.12</v>
+      </c>
+      <c r="J61">
+        <v>5213.2</v>
+      </c>
+      <c r="K61">
+        <v>51028.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>1002</v>
+      </c>
+      <c r="C62" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D62" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62">
+        <v>14.85</v>
+      </c>
+      <c r="H62">
+        <v>2285.73</v>
+      </c>
+      <c r="J62">
+        <v>5198.3500000000004</v>
+      </c>
+      <c r="K62">
+        <v>48742.57</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>1002</v>
+      </c>
+      <c r="C63" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D63" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" t="s">
+        <v>24</v>
+      </c>
+      <c r="F63" t="s">
+        <v>17</v>
+      </c>
+      <c r="G63">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="H63">
+        <v>2813.02</v>
+      </c>
+      <c r="J63">
+        <v>5181.75</v>
+      </c>
+      <c r="K63">
+        <v>45929.55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>1002</v>
+      </c>
+      <c r="C64" s="2">
+        <v>45815</v>
+      </c>
+      <c r="D64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" t="s">
+        <v>22</v>
+      </c>
+      <c r="F64" t="s">
+        <v>23</v>
+      </c>
+      <c r="G64">
+        <v>81.41</v>
+      </c>
+      <c r="H64">
+        <v>1555.02</v>
+      </c>
+      <c r="J64">
+        <v>5100.34</v>
+      </c>
+      <c r="K64">
+        <v>44374.53</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>1002</v>
+      </c>
+      <c r="C65" s="2">
+        <v>45815</v>
+      </c>
+      <c r="D65" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65">
+        <v>59.31</v>
+      </c>
+      <c r="H65">
+        <v>1818.74</v>
+      </c>
+      <c r="J65">
+        <v>5041.03</v>
+      </c>
+      <c r="K65">
+        <v>42555.79</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>1002</v>
+      </c>
+      <c r="C66" s="2">
+        <v>45815</v>
+      </c>
+      <c r="D66" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66">
+        <v>10.6</v>
+      </c>
+      <c r="H66">
+        <v>2242.4499999999998</v>
+      </c>
+      <c r="J66">
+        <v>5030.43</v>
+      </c>
+      <c r="K66">
+        <v>40313.339999999997</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>1002</v>
+      </c>
+      <c r="C67" s="2">
+        <v>45815</v>
+      </c>
+      <c r="D67" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67" t="s">
+        <v>17</v>
+      </c>
+      <c r="G67">
+        <v>17.920000000000002</v>
+      </c>
+      <c r="H67">
+        <v>2036.57</v>
+      </c>
+      <c r="J67">
+        <v>5012.51</v>
+      </c>
+      <c r="K67">
+        <v>38276.769999999997</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>1002</v>
+      </c>
+      <c r="C68" s="2">
+        <v>45816</v>
+      </c>
+      <c r="D68" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" t="s">
+        <v>20</v>
+      </c>
+      <c r="F68" t="s">
+        <v>21</v>
+      </c>
+      <c r="G68">
+        <v>22.71</v>
+      </c>
+      <c r="H68">
+        <v>1903.94</v>
+      </c>
+      <c r="J68">
+        <v>4989.8</v>
+      </c>
+      <c r="K68">
+        <v>36372.83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>1003</v>
+      </c>
+      <c r="C69" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D69" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" t="s">
+        <v>22</v>
+      </c>
+      <c r="F69" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69">
+        <v>90.83</v>
+      </c>
+      <c r="H69">
+        <v>2950.48</v>
+      </c>
+      <c r="J69">
+        <v>1909.17</v>
+      </c>
+      <c r="K69">
+        <v>97049.52</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>1003</v>
+      </c>
+      <c r="C70" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" t="s">
+        <v>20</v>
+      </c>
+      <c r="F70" t="s">
+        <v>21</v>
+      </c>
+      <c r="G70">
+        <v>39.58</v>
+      </c>
+      <c r="H70">
+        <v>2748.37</v>
+      </c>
+      <c r="J70">
+        <v>1869.59</v>
+      </c>
+      <c r="K70">
+        <v>94301.15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>1003</v>
+      </c>
+      <c r="C71" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D71" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" t="s">
+        <v>29</v>
+      </c>
+      <c r="F71" t="s">
+        <v>30</v>
+      </c>
+      <c r="G71">
+        <v>13.09</v>
+      </c>
+      <c r="H71">
+        <v>1916.64</v>
+      </c>
+      <c r="J71">
+        <v>1856.5</v>
+      </c>
+      <c r="K71">
+        <v>92384.51</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>1003</v>
+      </c>
+      <c r="C72" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D72" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" t="s">
+        <v>17</v>
+      </c>
+      <c r="G72">
+        <v>38.450000000000003</v>
+      </c>
+      <c r="H72">
+        <v>2477.73</v>
+      </c>
+      <c r="J72">
+        <v>1818.05</v>
+      </c>
+      <c r="K72">
+        <v>89906.78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>1003</v>
+      </c>
+      <c r="C73" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D73" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" t="s">
+        <v>20</v>
+      </c>
+      <c r="F73" t="s">
+        <v>21</v>
+      </c>
+      <c r="G73">
+        <v>15.01</v>
+      </c>
+      <c r="H73">
+        <v>1626.57</v>
+      </c>
+      <c r="J73">
+        <v>1803.04</v>
+      </c>
+      <c r="K73">
+        <v>88280.21</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>1003</v>
+      </c>
+      <c r="C74" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D74" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" t="s">
+        <v>15</v>
+      </c>
+      <c r="G74">
+        <v>21.67</v>
+      </c>
+      <c r="H74">
+        <v>2535.0700000000002</v>
+      </c>
+      <c r="J74">
+        <v>1781.37</v>
+      </c>
+      <c r="K74">
+        <v>85745.14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>1003</v>
+      </c>
+      <c r="C75" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D75" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" t="s">
+        <v>10</v>
+      </c>
+      <c r="F75" t="s">
+        <v>11</v>
+      </c>
+      <c r="G75">
+        <v>19.37</v>
+      </c>
+      <c r="H75">
+        <v>2556.0500000000002</v>
+      </c>
+      <c r="J75">
+        <v>1762</v>
+      </c>
+      <c r="K75">
+        <v>83189.09</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>1003</v>
+      </c>
+      <c r="C76" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D76" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" t="s">
+        <v>18</v>
+      </c>
+      <c r="F76" t="s">
+        <v>19</v>
+      </c>
+      <c r="G76">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="H76">
+        <v>1657.81</v>
+      </c>
+      <c r="J76">
+        <v>1745.42</v>
+      </c>
+      <c r="K76">
+        <v>81531.28</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>1003</v>
+      </c>
+      <c r="C77" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D77" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" t="s">
+        <v>16</v>
+      </c>
+      <c r="F77" t="s">
+        <v>17</v>
+      </c>
+      <c r="G77">
+        <v>17.53</v>
+      </c>
+      <c r="H77">
+        <v>2976.3</v>
+      </c>
+      <c r="J77">
+        <v>1727.89</v>
+      </c>
+      <c r="K77">
+        <v>78554.98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>1003</v>
+      </c>
+      <c r="C78" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" t="s">
+        <v>18</v>
+      </c>
+      <c r="F78" t="s">
+        <v>19</v>
+      </c>
+      <c r="G78">
+        <v>49.48</v>
+      </c>
+      <c r="H78">
+        <v>2878.77</v>
+      </c>
+      <c r="J78">
+        <v>1678.41</v>
+      </c>
+      <c r="K78">
+        <v>75676.210000000006</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>1003</v>
+      </c>
+      <c r="C79" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D79" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" t="s">
+        <v>24</v>
+      </c>
+      <c r="F79" t="s">
+        <v>17</v>
+      </c>
+      <c r="G79">
+        <v>12.37</v>
+      </c>
+      <c r="H79">
+        <v>2223.7199999999998</v>
+      </c>
+      <c r="J79">
+        <v>1666.04</v>
+      </c>
+      <c r="K79">
+        <v>73452.490000000005</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>1003</v>
+      </c>
+      <c r="C80" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D80" t="s">
+        <v>25</v>
+      </c>
+      <c r="E80" t="s">
+        <v>26</v>
+      </c>
+      <c r="F80" t="s">
+        <v>27</v>
+      </c>
+      <c r="G80">
+        <v>4000</v>
+      </c>
+      <c r="H80">
+        <v>2291.62</v>
+      </c>
+      <c r="J80">
+        <v>5666.04</v>
+      </c>
+      <c r="K80">
+        <v>75744.11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>1003</v>
+      </c>
+      <c r="C81" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D81" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" t="s">
+        <v>10</v>
+      </c>
+      <c r="F81" t="s">
+        <v>11</v>
+      </c>
+      <c r="G81">
+        <v>26.08</v>
+      </c>
+      <c r="H81">
+        <v>2583.08</v>
+      </c>
+      <c r="J81">
+        <v>5639.96</v>
+      </c>
+      <c r="K81">
+        <v>73161.03</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>1003</v>
+      </c>
+      <c r="C82" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D82" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" t="s">
+        <v>28</v>
+      </c>
+      <c r="F82" t="s">
+        <v>19</v>
+      </c>
+      <c r="G82">
+        <v>20.46</v>
+      </c>
+      <c r="H82">
+        <v>2336.81</v>
+      </c>
+      <c r="J82">
+        <v>5619.5</v>
+      </c>
+      <c r="K82">
+        <v>70824.22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>1003</v>
+      </c>
+      <c r="C83" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D83" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" t="s">
+        <v>28</v>
+      </c>
+      <c r="F83" t="s">
+        <v>11</v>
+      </c>
+      <c r="G83">
+        <v>24.08</v>
+      </c>
+      <c r="H83">
+        <v>1895.92</v>
+      </c>
+      <c r="J83">
+        <v>5595.42</v>
+      </c>
+      <c r="K83">
+        <v>68928.3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>1003</v>
+      </c>
+      <c r="C84" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D84" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" t="s">
+        <v>16</v>
+      </c>
+      <c r="F84" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84">
+        <v>29.05</v>
+      </c>
+      <c r="H84">
+        <v>2400.85</v>
+      </c>
+      <c r="J84">
+        <v>5566.37</v>
+      </c>
+      <c r="K84">
+        <v>66527.45</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>1003</v>
+      </c>
+      <c r="C85" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D85" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" t="s">
+        <v>24</v>
+      </c>
+      <c r="F85" t="s">
+        <v>19</v>
+      </c>
+      <c r="G85">
+        <v>97.93</v>
+      </c>
+      <c r="H85">
+        <v>1564.42</v>
+      </c>
+      <c r="J85">
+        <v>5468.44</v>
+      </c>
+      <c r="K85">
+        <v>64963.03</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>1003</v>
+      </c>
+      <c r="C86" s="2">
+        <v>45813</v>
+      </c>
+      <c r="D86" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" t="s">
+        <v>22</v>
+      </c>
+      <c r="F86" t="s">
+        <v>19</v>
+      </c>
+      <c r="G86">
+        <v>21.43</v>
+      </c>
+      <c r="H86">
+        <v>2442.5300000000002</v>
+      </c>
+      <c r="J86">
+        <v>5447.01</v>
+      </c>
+      <c r="K86">
+        <v>62520.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>1003</v>
+      </c>
+      <c r="C87" s="2">
+        <v>45813</v>
+      </c>
+      <c r="D87" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" t="s">
+        <v>28</v>
+      </c>
+      <c r="F87" t="s">
+        <v>30</v>
+      </c>
+      <c r="G87">
+        <v>87.64</v>
+      </c>
+      <c r="H87">
+        <v>2090.3200000000002</v>
+      </c>
+      <c r="J87">
+        <v>5359.37</v>
+      </c>
+      <c r="K87">
+        <v>60430.18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>1003</v>
+      </c>
+      <c r="C88" s="2">
+        <v>45813</v>
+      </c>
+      <c r="D88" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" t="s">
+        <v>14</v>
+      </c>
+      <c r="F88" t="s">
+        <v>21</v>
+      </c>
+      <c r="G88">
+        <v>12.98</v>
+      </c>
+      <c r="H88">
+        <v>2113.33</v>
+      </c>
+      <c r="J88">
+        <v>5346.39</v>
+      </c>
+      <c r="K88">
+        <v>58316.85</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>1003</v>
+      </c>
+      <c r="C89" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D89" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" t="s">
+        <v>20</v>
+      </c>
+      <c r="F89" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89">
+        <v>12.9</v>
+      </c>
+      <c r="H89">
+        <v>1647.84</v>
+      </c>
+      <c r="J89">
+        <v>5333.49</v>
+      </c>
+      <c r="K89">
+        <v>56669.01</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>1003</v>
+      </c>
+      <c r="C90" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D90" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" t="s">
+        <v>24</v>
+      </c>
+      <c r="F90" t="s">
+        <v>17</v>
+      </c>
+      <c r="G90">
+        <v>19.36</v>
+      </c>
+      <c r="H90">
+        <v>2957.45</v>
+      </c>
+      <c r="J90">
+        <v>5314.13</v>
+      </c>
+      <c r="K90">
+        <v>53711.56</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>1003</v>
+      </c>
+      <c r="C91" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D91" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" t="s">
+        <v>20</v>
+      </c>
+      <c r="F91" t="s">
+        <v>21</v>
+      </c>
+      <c r="G91">
+        <v>34.03</v>
+      </c>
+      <c r="H91">
+        <v>1689.51</v>
+      </c>
+      <c r="J91">
+        <v>5280.1</v>
+      </c>
+      <c r="K91">
+        <v>52022.05</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>1003</v>
+      </c>
+      <c r="C92" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D92" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" t="s">
+        <v>14</v>
+      </c>
+      <c r="F92" t="s">
+        <v>15</v>
+      </c>
+      <c r="G92">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="H92">
+        <v>2034.88</v>
+      </c>
+      <c r="J92">
+        <v>5214.8900000000003</v>
+      </c>
+      <c r="K92">
+        <v>49987.17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>1003</v>
+      </c>
+      <c r="C93" s="2">
+        <v>45815</v>
+      </c>
+      <c r="D93" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" t="s">
+        <v>29</v>
+      </c>
+      <c r="F93" t="s">
+        <v>30</v>
+      </c>
+      <c r="G93">
+        <v>16.47</v>
+      </c>
+      <c r="H93">
+        <v>2083.7399999999998</v>
+      </c>
+      <c r="J93">
+        <v>5198.42</v>
+      </c>
+      <c r="K93">
+        <v>47903.43</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>1003</v>
+      </c>
+      <c r="C94" s="2">
+        <v>45815</v>
+      </c>
+      <c r="D94" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" t="s">
+        <v>11</v>
+      </c>
+      <c r="G94">
+        <v>12.09</v>
+      </c>
+      <c r="H94">
+        <v>1622.88</v>
+      </c>
+      <c r="J94">
+        <v>5186.33</v>
+      </c>
+      <c r="K94">
+        <v>46280.55</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>1003</v>
+      </c>
+      <c r="C95" s="2">
+        <v>45815</v>
+      </c>
+      <c r="D95" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" t="s">
+        <v>12</v>
+      </c>
+      <c r="F95" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95">
+        <v>23.28</v>
+      </c>
+      <c r="H95">
+        <v>2477.67</v>
+      </c>
+      <c r="J95">
+        <v>5163.05</v>
+      </c>
+      <c r="K95">
+        <v>43802.879999999997</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>1003</v>
+      </c>
+      <c r="C96" s="2">
+        <v>45815</v>
+      </c>
+      <c r="D96" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" t="s">
+        <v>18</v>
+      </c>
+      <c r="F96" t="s">
+        <v>19</v>
+      </c>
+      <c r="G96">
+        <v>15.59</v>
+      </c>
+      <c r="H96">
+        <v>1880.66</v>
+      </c>
+      <c r="J96">
+        <v>5147.46</v>
+      </c>
+      <c r="K96">
+        <v>41922.22</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>1003</v>
+      </c>
+      <c r="C97" s="2">
+        <v>45815</v>
+      </c>
+      <c r="D97" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" t="s">
+        <v>22</v>
+      </c>
+      <c r="F97" t="s">
+        <v>23</v>
+      </c>
+      <c r="G97">
+        <v>54.88</v>
+      </c>
+      <c r="H97">
+        <v>2523.02</v>
+      </c>
+      <c r="J97">
+        <v>5092.58</v>
+      </c>
+      <c r="K97">
+        <v>39399.199999999997</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>1003</v>
+      </c>
+      <c r="C98" s="2">
+        <v>45816</v>
+      </c>
+      <c r="D98" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98">
+        <v>20.190000000000001</v>
+      </c>
+      <c r="H98">
+        <v>2916.29</v>
+      </c>
+      <c r="J98">
+        <v>5072.3900000000003</v>
+      </c>
+      <c r="K98">
+        <v>36482.910000000003</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>1003</v>
+      </c>
+      <c r="C99" s="2">
+        <v>45817</v>
+      </c>
+      <c r="D99" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" t="s">
+        <v>22</v>
+      </c>
+      <c r="F99" t="s">
+        <v>23</v>
+      </c>
+      <c r="G99">
+        <v>18.16</v>
+      </c>
+      <c r="H99">
+        <v>2740.49</v>
+      </c>
+      <c r="J99">
+        <v>5054.2299999999996</v>
+      </c>
+      <c r="K99">
+        <v>33742.42</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>1004</v>
+      </c>
+      <c r="C100" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D100" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" t="s">
+        <v>29</v>
+      </c>
+      <c r="F100" t="s">
+        <v>30</v>
+      </c>
+      <c r="G100">
+        <v>13.09</v>
+      </c>
+      <c r="H100">
+        <v>1856.08</v>
+      </c>
+      <c r="J100">
+        <v>1986.91</v>
+      </c>
+      <c r="K100">
+        <v>98143.92</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>1004</v>
+      </c>
+      <c r="C101" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D101" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" t="s">
+        <v>29</v>
+      </c>
+      <c r="F101" t="s">
+        <v>30</v>
+      </c>
+      <c r="G101">
+        <v>22.53</v>
+      </c>
+      <c r="H101">
+        <v>2292.48</v>
+      </c>
+      <c r="J101">
+        <v>1964.38</v>
+      </c>
+      <c r="K101">
+        <v>95851.44</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>1004</v>
+      </c>
+      <c r="C102" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D102" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" t="s">
+        <v>24</v>
+      </c>
+      <c r="F102" t="s">
+        <v>17</v>
+      </c>
+      <c r="G102">
+        <v>59.83</v>
+      </c>
+      <c r="H102">
+        <v>1904.08</v>
+      </c>
+      <c r="J102">
+        <v>1904.55</v>
+      </c>
+      <c r="K102">
+        <v>93947.36</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>1004</v>
+      </c>
+      <c r="C103" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D103" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" t="s">
+        <v>20</v>
+      </c>
+      <c r="F103" t="s">
+        <v>21</v>
+      </c>
+      <c r="G103">
+        <v>10.06</v>
+      </c>
+      <c r="H103">
+        <v>2993.88</v>
+      </c>
+      <c r="J103">
+        <v>1894.49</v>
+      </c>
+      <c r="K103">
+        <v>90953.48</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>1004</v>
+      </c>
+      <c r="C104" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D104" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" t="s">
+        <v>28</v>
+      </c>
+      <c r="F104" t="s">
+        <v>19</v>
+      </c>
+      <c r="G104">
+        <v>43.73</v>
+      </c>
+      <c r="H104">
+        <v>1981.09</v>
+      </c>
+      <c r="J104">
+        <v>1850.76</v>
+      </c>
+      <c r="K104">
+        <v>88972.39</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>1004</v>
+      </c>
+      <c r="C105" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D105" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" t="s">
+        <v>16</v>
+      </c>
+      <c r="F105" t="s">
+        <v>17</v>
+      </c>
+      <c r="G105">
+        <v>22.7</v>
+      </c>
+      <c r="H105">
+        <v>2606.12</v>
+      </c>
+      <c r="J105">
+        <v>1828.06</v>
+      </c>
+      <c r="K105">
+        <v>86366.27</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>1004</v>
+      </c>
+      <c r="C106" s="2">
+        <v>45810</v>
+      </c>
+      <c r="D106" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" t="s">
+        <v>28</v>
+      </c>
+      <c r="F106" t="s">
+        <v>19</v>
+      </c>
+      <c r="G106">
+        <v>12.72</v>
+      </c>
+      <c r="H106">
+        <v>2285.73</v>
+      </c>
+      <c r="J106">
+        <v>1815.34</v>
+      </c>
+      <c r="K106">
+        <v>84080.54</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>1004</v>
+      </c>
+      <c r="C107" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D107" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" t="s">
+        <v>20</v>
+      </c>
+      <c r="F107" t="s">
+        <v>21</v>
+      </c>
+      <c r="G107">
+        <v>22.55</v>
+      </c>
+      <c r="H107">
+        <v>2813.02</v>
+      </c>
+      <c r="J107">
+        <v>1792.79</v>
+      </c>
+      <c r="K107">
+        <v>81267.520000000004</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>1004</v>
+      </c>
+      <c r="C108" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D108" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" t="s">
+        <v>14</v>
+      </c>
+      <c r="F108" t="s">
+        <v>15</v>
+      </c>
+      <c r="G108">
+        <v>13.07</v>
+      </c>
+      <c r="H108">
+        <v>1555.02</v>
+      </c>
+      <c r="J108">
+        <v>1779.72</v>
+      </c>
+      <c r="K108">
+        <v>79712.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>1004</v>
+      </c>
+      <c r="C109" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D109" t="s">
+        <v>25</v>
+      </c>
+      <c r="E109" t="s">
+        <v>26</v>
+      </c>
+      <c r="F109" t="s">
+        <v>27</v>
+      </c>
+      <c r="G109">
+        <v>4000</v>
+      </c>
+      <c r="H109">
+        <v>1818.74</v>
+      </c>
+      <c r="J109">
+        <v>5779.72</v>
+      </c>
+      <c r="K109">
+        <v>81531.240000000005</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>1004</v>
+      </c>
+      <c r="C110" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D110" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110" t="s">
+        <v>18</v>
+      </c>
+      <c r="F110" t="s">
+        <v>19</v>
+      </c>
+      <c r="G110">
+        <v>11.1</v>
+      </c>
+      <c r="H110">
+        <v>2242.4499999999998</v>
+      </c>
+      <c r="J110">
+        <v>5768.62</v>
+      </c>
+      <c r="K110">
+        <v>79288.789999999994</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>1004</v>
+      </c>
+      <c r="C111" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D111" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" t="s">
+        <v>18</v>
+      </c>
+      <c r="F111" t="s">
+        <v>19</v>
+      </c>
+      <c r="G111">
+        <v>24.79</v>
+      </c>
+      <c r="H111">
+        <v>2036.57</v>
+      </c>
+      <c r="J111">
+        <v>5743.83</v>
+      </c>
+      <c r="K111">
+        <v>77252.22</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>1004</v>
+      </c>
+      <c r="C112" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D112" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" t="s">
+        <v>29</v>
+      </c>
+      <c r="F112" t="s">
+        <v>30</v>
+      </c>
+      <c r="G112">
+        <v>77.209999999999994</v>
+      </c>
+      <c r="H112">
+        <v>1903.94</v>
+      </c>
+      <c r="J112">
+        <v>5666.62</v>
+      </c>
+      <c r="K112">
+        <v>75348.28</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>1004</v>
+      </c>
+      <c r="C113" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D113" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" t="s">
+        <v>10</v>
+      </c>
+      <c r="F113" t="s">
+        <v>11</v>
+      </c>
+      <c r="G113">
+        <v>35.43</v>
+      </c>
+      <c r="H113">
+        <v>2950.48</v>
+      </c>
+      <c r="J113">
+        <v>5631.19</v>
+      </c>
+      <c r="K113">
+        <v>72397.8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>1004</v>
+      </c>
+      <c r="C114" s="2">
+        <v>45811</v>
+      </c>
+      <c r="D114" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" t="s">
+        <v>24</v>
+      </c>
+      <c r="F114" t="s">
+        <v>17</v>
+      </c>
+      <c r="G114">
+        <v>17.77</v>
+      </c>
+      <c r="H114">
+        <v>2748.37</v>
+      </c>
+      <c r="J114">
+        <v>5613.42</v>
+      </c>
+      <c r="K114">
+        <v>69649.429999999993</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>1004</v>
+      </c>
+      <c r="C115" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D115" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" t="s">
+        <v>29</v>
+      </c>
+      <c r="F115" t="s">
+        <v>30</v>
+      </c>
+      <c r="G115">
+        <v>24.56</v>
+      </c>
+      <c r="H115">
+        <v>1916.64</v>
+      </c>
+      <c r="J115">
+        <v>5588.86</v>
+      </c>
+      <c r="K115">
+        <v>67732.789999999994</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>1004</v>
+      </c>
+      <c r="C116" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D116" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" t="s">
+        <v>24</v>
+      </c>
+      <c r="F116" t="s">
+        <v>17</v>
+      </c>
+      <c r="G116">
+        <v>24.31</v>
+      </c>
+      <c r="H116">
+        <v>2477.73</v>
+      </c>
+      <c r="J116">
+        <v>5564.55</v>
+      </c>
+      <c r="K116">
+        <v>65255.06</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>1004</v>
+      </c>
+      <c r="C117" s="2">
+        <v>45812</v>
+      </c>
+      <c r="D117" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" t="s">
+        <v>10</v>
+      </c>
+      <c r="F117" t="s">
+        <v>11</v>
+      </c>
+      <c r="G117">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="H117">
+        <v>1626.57</v>
+      </c>
+      <c r="J117">
+        <v>5544.56</v>
+      </c>
+      <c r="K117">
+        <v>63628.49</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>1004</v>
+      </c>
+      <c r="C118" s="2">
+        <v>45813</v>
+      </c>
+      <c r="D118" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" t="s">
+        <v>12</v>
+      </c>
+      <c r="F118" t="s">
+        <v>17</v>
+      </c>
+      <c r="G118">
+        <v>91.64</v>
+      </c>
+      <c r="H118">
+        <v>2535.0700000000002</v>
+      </c>
+      <c r="J118">
+        <v>5452.92</v>
+      </c>
+      <c r="K118">
+        <v>61093.42</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>1004</v>
+      </c>
+      <c r="C119" s="2">
+        <v>45813</v>
+      </c>
+      <c r="D119" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" t="s">
+        <v>16</v>
+      </c>
+      <c r="F119" t="s">
+        <v>17</v>
+      </c>
+      <c r="G119">
+        <v>23.81</v>
+      </c>
+      <c r="H119">
+        <v>2556.0500000000002</v>
+      </c>
+      <c r="J119">
+        <v>5429.11</v>
+      </c>
+      <c r="K119">
+        <v>58537.37</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>1004</v>
+      </c>
+      <c r="C120" s="2">
+        <v>45813</v>
+      </c>
+      <c r="D120" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" t="s">
+        <v>10</v>
+      </c>
+      <c r="F120" t="s">
+        <v>15</v>
+      </c>
+      <c r="G120">
+        <v>10.45</v>
+      </c>
+      <c r="H120">
+        <v>1657.81</v>
+      </c>
+      <c r="J120">
+        <v>5418.66</v>
+      </c>
+      <c r="K120">
+        <v>56879.56</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>1004</v>
+      </c>
+      <c r="C121" s="2">
+        <v>45813</v>
+      </c>
+      <c r="D121" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" t="s">
+        <v>10</v>
+      </c>
+      <c r="F121" t="s">
+        <v>19</v>
+      </c>
+      <c r="G121">
+        <v>78.47</v>
+      </c>
+      <c r="H121">
+        <v>2976.3</v>
+      </c>
+      <c r="J121">
+        <v>5340.19</v>
+      </c>
+      <c r="K121">
+        <v>53903.26</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>1004</v>
+      </c>
+      <c r="C122" s="2">
+        <v>45813</v>
+      </c>
+      <c r="D122" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" t="s">
+        <v>16</v>
+      </c>
+      <c r="F122" t="s">
+        <v>11</v>
+      </c>
+      <c r="G122">
+        <v>10.61</v>
+      </c>
+      <c r="H122">
+        <v>2878.77</v>
+      </c>
+      <c r="J122">
+        <v>5329.58</v>
+      </c>
+      <c r="K122">
+        <v>51024.49</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>1004</v>
+      </c>
+      <c r="C123" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D123" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" t="s">
+        <v>16</v>
+      </c>
+      <c r="F123" t="s">
+        <v>19</v>
+      </c>
+      <c r="G123">
+        <v>17.28</v>
+      </c>
+      <c r="H123">
+        <v>2223.7199999999998</v>
+      </c>
+      <c r="J123">
+        <v>5312.3</v>
+      </c>
+      <c r="K123">
+        <v>48800.77</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>1004</v>
+      </c>
+      <c r="C124" s="2">
+        <v>45814</v>
+      </c>
+      <c r="D124" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" t="s">
+        <v>28</v>
+      </c>
+      <c r="F124" t="s">
+        <v>17</v>
+      </c>
+      <c r="G124">
+        <v>10.23</v>
+      </c>
+      <c r="H124">
+        <v>2291.62</v>
+      </c>
+      <c r="J124">
+        <v>5302.07</v>
+      </c>
+      <c r="K124">
+        <v>46509.15</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>